--- a/Luban/Config/Datas/#ZoneConfig.xlsx
+++ b/Luban/Config/Datas/#ZoneConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D4BCE7-A8E1-4C3F-BFCE-B52277417ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A538DAC7-EDB2-4066-82F6-C7B971742C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="3825" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -520,7 +520,7 @@
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="19.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.25" style="1" bestFit="1" customWidth="1"/>
